--- a/_103_CharacterSkills.xlsx
+++ b/_103_CharacterSkills.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\UnityPortfolioProjectTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NextHorizonTables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6D3F5C-4481-4A41-A811-016A9FEF784F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E179CAEA-D58B-46B6-9910-ABFE2DD0BBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{8996C81C-FF45-4FA2-B6CE-365CE91B1C33}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>parameter9</t>
-  </si>
-  <si>
-    <t>parameter10</t>
   </si>
   <si>
     <t>ESkillType</t>
@@ -519,14 +516,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB77E38-BF09-42DC-A18A-223E5D5C39AB}">
-  <dimension ref="A2:O54"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:N54"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="36" width="12.5703125" style="4" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="36" width="12.5625" style="4" customWidth="1"/>
+    <col min="37" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +534,7 @@
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>5</v>
@@ -569,11 +566,8 @@
       <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -584,7 +578,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>2</v>
@@ -616,11 +610,8 @@
       <c r="N3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A4" s="2">
         <v>1030001</v>
       </c>
@@ -631,10 +622,10 @@
         <v>9050002</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F4" s="2">
         <v>0</v>
@@ -663,11 +654,8 @@
       <c r="N4" s="2">
         <v>0</v>
       </c>
-      <c r="O4" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A5" s="3">
         <v>1030002</v>
       </c>
@@ -678,16 +666,16 @@
         <v>9050004</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F5" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -710,11 +698,8 @@
       <c r="N5" s="3">
         <v>0</v>
       </c>
-      <c r="O5" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A6" s="2">
         <v>1030003</v>
       </c>
@@ -725,13 +710,13 @@
         <v>9050006</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -757,11 +742,8 @@
       <c r="N6" s="2">
         <v>0</v>
       </c>
-      <c r="O6" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A7" s="3">
         <v>1030004</v>
       </c>
@@ -772,10 +754,10 @@
         <v>9050008</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F7" s="3">
         <v>0</v>
@@ -804,11 +786,8 @@
       <c r="N7" s="3">
         <v>0</v>
       </c>
-      <c r="O7" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A8" s="2">
         <v>1030005</v>
       </c>
@@ -819,10 +798,10 @@
         <v>9050010</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F8" s="2">
         <v>0</v>
@@ -851,11 +830,8 @@
       <c r="N8" s="2">
         <v>0</v>
       </c>
-      <c r="O8" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A9" s="3">
         <v>1030006</v>
       </c>
@@ -866,10 +842,10 @@
         <v>9050012</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -898,11 +874,8 @@
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
         <v>1030007</v>
       </c>
@@ -913,10 +886,10 @@
         <v>9050014</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F10" s="2">
         <v>0</v>
@@ -945,11 +918,8 @@
       <c r="N10" s="2">
         <v>0</v>
       </c>
-      <c r="O10" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A11" s="3">
         <v>1030008</v>
       </c>
@@ -960,16 +930,16 @@
         <v>9050016</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F11" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" s="3">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H11" s="3">
         <v>0</v>
@@ -992,11 +962,8 @@
       <c r="N11" s="3">
         <v>0</v>
       </c>
-      <c r="O11" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2">
         <v>1030009</v>
       </c>
@@ -1007,7 +974,7 @@
         <v>9050018</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2">
         <v>0</v>
@@ -1039,52 +1006,49 @@
       <c r="N12" s="2">
         <v>0</v>
       </c>
-      <c r="O12" s="2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="15" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
-    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="13" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="15" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="17" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="18" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="19" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="20" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="21" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="22" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="23" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="24" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="25" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="26" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="27" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="28" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="29" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="30" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="31" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="32" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="33" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="34" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="35" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="36" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="37" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="38" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="39" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="40" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="41" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="42" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="43" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="44" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="45" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="46" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="47" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="48" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="49" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="50" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="51" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="52" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="53" s="3" customFormat="1" x14ac:dyDescent="0.6"/>
+    <row r="54" s="2" customFormat="1" x14ac:dyDescent="0.6"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
